--- a/business_forms/048_customer_inquiry_communication_form--business_forms.xlsx
+++ b/business_forms/048_customer_inquiry_communication_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,20 +525,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +552,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>customer_inquiry_details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Contact Method</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How can we contact you?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Inquiry or Complaint</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe your problem</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form_4</t>
+          <t>satisfactory_service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Satisfactory Service</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Did we provide satisfactory service?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form_5</t>
+          <t>date_of_inquiry_or_complaint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Date of Incident</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(mm/dd/yyyy)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +655,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form_6</t>
+          <t>time_of_contact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Time of Contact</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(HH -MM am/pm)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,11 +687,69 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter your email address or phone number</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>customer_inquiry_communication_form_8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Preferred Method of Communication</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>customer_inquiry_communication_form_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Is there anything else you'd like to add?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -684,11 +766,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -712,34 +794,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form_3_choices</t>
+          <t>customer_inquiry_communication_form_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>email</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_inquiry_communication_form_3_choices</t>
+          <t>customer_inquiry_communication_form_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>customer_inquiry_communication_form_2_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>customer_inquiry_communication_form_8_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>customer_inquiry_communication_form_8_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>customer_inquiry_communication_form_8_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mail</t>
         </is>
       </c>
     </row>
